--- a/business_forms/034_playground_equipment_complaint_form--business_forms.xlsx
+++ b/business_forms/034_playground_equipment_complaint_form--business_forms.xlsx
@@ -1,15 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -32,7 +31,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -43,12 +42,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="004472C4"/>
         <bgColor rgb="004472C4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="0070AD47"/>
-        <bgColor rgb="0070AD47"/>
       </patternFill>
     </fill>
   </fills>
@@ -64,12 +57,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -437,11 +427,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="39" customWidth="1" min="2" max="2"/>
     <col width="37" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -520,7 +510,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>playground_equipment_complaint_form_1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -538,17 +528,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>playground_equipment_complaint_form_2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Contact Information</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -566,12 +556,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>playground_equipment_complaint_form_3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Equipment Details</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -589,12 +579,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>playground_equipment_complaint_form_4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>Issue Description</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -612,12 +602,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>playground_equipment_complaint_form_5</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Report Location</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -635,108 +625,16 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>playground_equipment_complaint_form_6</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Additional Information</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>phone</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Phone</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -748,76 +646,6 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
-    <col width="17" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>list_name</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>label</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>category_choices</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>business_forms</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Business Forms</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>category_choices</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>complaint_forms</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Complaint Forms</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
